--- a/pacjenci/EDWARD DRAPAŁA.xlsx
+++ b/pacjenci/EDWARD DRAPAŁA.xlsx
@@ -483,7 +483,11 @@
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>Do oceny</t>
@@ -523,7 +527,11 @@
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>Do oceny</t>
@@ -563,7 +571,11 @@
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>Do oceny</t>

--- a/pacjenci/EDWARD DRAPAŁA.xlsx
+++ b/pacjenci/EDWARD DRAPAŁA.xlsx
@@ -413,191 +413,143 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>24.05.2021</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Chłoniak nieziarniczy rozlany. Ocena stopnia zaawansowania.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 60min od podania 18F-FDG. Glikemia: 88mg%</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Aktywne metabolicznie węzły chłonne wnęki płuca prawego średnicy do 14mm, SUV max 5,4.  Wnęka płuca lewego SUV max 3,6. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Pęcherz rozedmowy 10mm w segm. 1+2 płuca lewego, nadprzeponowo niewielkie pasmowate zmiany bliznowato-włókniste.  Brzuch i miednica: Aktywny metabolicznie naciek obejmujący część przedodźwiernikowej żołądka, dwunastnicę, przyległy miąższ płata lewego wątroby i pęcherzyka żółciowego na łącznym obszarze wg PET 162x86x74mm, SUV max do 33,0. Drobny aktywny metabolicznie obszar w żołądku na krzywiźnie większej średnicy wg PET 33mm, SUV max 6,5. Liczne aktywne metabolicznie obszary w topografii jelit średnicy wg PET do 46mm, SUV max do 16,3 - w pierwszej kolejności nacieki chłoniakowe Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Prostata wielkości 58x59mm.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa z cechami dyskopatii wielopoziomowo. Zmiany zwyrodnieniowe w stawach ramiennych, mniej nasilone w stawach biodrowych.  Inne: Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax 1,6, Prawy płat wątroby SUVmax do 3,0.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono rozległy naciek chłoniakowy obejmujący część przedodźwiernikową żołądka, dwunastnicę, przyległy miąższ płata lewego wątroby i pęcherzyka żółciowego, aktywne metabolicznie nacieki w obrębie jelit, żołądka oraz aktywne metabolicznie węzły chłonne wnęki płuca prawego.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>33</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>07.09.2021</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Chłoniak nieziarniczy rozlany. Ocena odpowiedzi po 4 cyklach chemioterapii.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57min od podania 18F-FDG. Glikemia: 92mg%.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony,  miernie nasilony zanik korowo-podkorowy mózgu. Niewielkie okrężne zgrubienia błony śluzowej w lewej zatoce szczękowej.  Klatka piersiowa i śródpiersie: Pobudzony metabolicznie obszar we wnęce płuca prawego średnicy 10mm, SUV max 3,5 - węzeł chłonny? Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Aorta wstępująca o szerokości 42mm. Pęcherz rozedmowy śr. 14mm w segm. 1+2/3 płuca lewego. Drobne obwodowe zmiany włókniste w płacie górnym płuca prawego i lewego. Wydatne pasmowate zmiany włókniste obustronnie nadprzeponowo. Obszary o typie "mlecznej szyby" nadprzeponowo w płucu prawym.  Brzuch i miednica: Aktywny metabolicznie obszar w części przedodźwiernikowej żołądka, wielkości 29mm wg PET, SUV max 5,9, ze zwężeniem kanału odźwiernika i zaleganiem treści żołądkowej. Niejednorodny metabolizm FDG w wątrobie zwłaszcza w s. 4 z wyróżniającym się podtorebkowo obszarem wielkości 10mm wg PET, SUV max 4,7- do oceny w badaniu TK/MR z kontrastem dożylnym. Rozlana i odcinkowo zwiększona aktywnośc metaboliczna w topografii pętli jelitowych - do oceny w kolonoskopii ze względu na opisywane poprzednio nacieki chłoniakowe.  Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nerki o "pozaciąganych" pozapalnie obrysach. Drobny uwapniony konkrement w UKM-ie nerki prawej. Prostata powiększona, wielkości: 65x59mm, wpukla się w obręb pęcherza moczowego - do kontroli urologicznej.  Układ kostny: Zwiększony metabolizm FDG w układzie kostnym- w pierwszej kolejności w związku ze stosowanym leczeniem. Nasilone zmiany zwyrodnieniowo-wytwórcze kręgosłupa.  Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa. Wielopoziomowo nierówne obrysy blaszek granicznych trzonów kręgowych i drobne guzki Schmorla. Drobna spondylolisteza przednia na poziomie L4/L5. Zmiany zwyrodnieniowo-wywtórcze w małych stawach mizykręgowych i w stawach żebrowo-poprzecznych. Zmiany zwyrodnieniowe w stawach ramiennych oraz mniej nasilone w stawach biodrowych. Wydatna wyspa kostna w przymostkowym końcu prawego obojczyka.  Inne: Nasilona miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax do 2,5; Prawy płat wątroby SUVmax do 3,4.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono dobrą odpowiedź metaboliczną choroby chłoniakowej na stosowane leczenie. Aktywny metabolicznie obszar w części przedodźwiernikowej żołądka - masa resztkowa?- do weryfikacji w gastroskopii. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>5.9</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>22.11.2021</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Chłoniak nieziarniczy rozlany. Ocena remisji choroby.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 58 min od podania 18F-FDG. Glikemia: 112 mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Drobny obszar wzmożonego metabolizmu FDG w śliniance przyusznej lewej średnicy 10 mm wg PET SUV max 3,9-węzeł własny? -  do kontroli w USG. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony,  miernie nasilony zanik korowo-podkorowy mózgu. Dyskretne zgrubienia błony śluzowej w zachyłku zębodołowym lewej zatoki szczękowej.  Klatka piersiowa i śródpiersie: Wzmożony metabolizm FDG we wnęce płuca prawego SUV max do 5,8 - w stosunku do wnęki płuca lewego SUV max do 3,4. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Znacznego stopnia zaleganie treści płynnej w żołądku [ze znacznym jego poszerzeniem - żołądek wypełnia w znacznym stopniu nadbrzusze i śródbrzusze oraz z pogrubieniem ściany w części przedodźwiernikowej i okolicy odźwiernika] oraz w 1/2 dolnej części przełyku [z jego poszerzeniem do 38mm] - celowa kontrola gastrologiczna/gastroskopowa. Aorta wstępująca o szerokości 42mm. Pęcherz rozedmowy śr. 14mm w segm. 1+2/3 płuca lewego. Ok. 3,5mm obwodowy uwapniony guzek w segm. 3 płuca prawego. Drobne obwodowe zmiany włókniste i pojedyncze drobnoguzkowe w płacie górnym płuca prawego i lewego. Niewielkie zmiany włókniste w segm. 5 obu płuc. Wydatne pasmowate zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Aktywny metabolicznie naciek w topografii połączenia odbytniczo-esiczego na obszarze wielkości 15x26 mm wg PET SUV max 14,3 - do pilnej weryfikacji w badaniu endoskopowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nerki o "pozaciąganych" pozapalnie obrysach. Drobny uwapniony konkrement w UKM-ie nerki prawej. Prostata powiększona, wielkości: 65x59mm, wpukla się w obręb pęcherza moczowego - do kontroli urologicznej.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Nasilone zmiany zwyrodnieniowo-wytwórcze kręgosłupa.  Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa.  Wielopoziomowo nierówne obrysy blaszek granicznych trzonów kręgowych i drobne guzki Schmorla. Drobna spondylolisteza przednia na poziomie L4/L5. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Zmiany zwyrodnieniowe w stawach ramiennych oraz mniej nasilone w stawach biodrowych. Wydatna wyspa kostna w przymostkowym końcu prawego obojczyka.  Inne: Nasilona miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax do 2,1; Prawy płat wątroby SUVmax do 3,1.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnego metabolicznie nacieku w topografii połączenia odbytniczo-esiczego - do pilnej weryfikacji w badaniu endoskopowym. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>14.3</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/EDWARD DRAPAŁA.xlsx
+++ b/pacjenci/EDWARD DRAPAŁA.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 60min od podania 18F-FDG. Glikemia: 88mg%</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Aktywne metabolicznie węzły chłonne wnęki płuca prawego średnicy do 14mm, SUV max 5,4.  Wnęka płuca lewego SUV max 3,6. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Pęcherz rozedmowy 10mm w segm. 1+2 płuca lewego, nadprzeponowo niewielkie pasmowate zmiany bliznowato-włókniste.  Brzuch i miednica: Aktywny metabolicznie naciek obejmujący część przedodźwiernikowej żołądka, dwunastnicę, przyległy miąższ płata lewego wątroby i pęcherzyka żółciowego na łącznym obszarze wg PET 162x86x74mm, SUV max do 33,0. Drobny aktywny metabolicznie obszar w żołądku na krzywiźnie większej średnicy wg PET 33mm, SUV max 6,5. Liczne aktywne metabolicznie obszary w topografii jelit średnicy wg PET do 46mm, SUV max do 16,3 - w pierwszej kolejności nacieki chłoniakowe Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Prostata wielkości 58x59mm.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa z cechami dyskopatii wielopoziomowo. Zmiany zwyrodnieniowe w stawach ramiennych, mniej nasilone w stawach biodrowych.  Inne: Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax 1,6, Prawy płat wątroby SUVmax do 3,0.</t>
+          <t>88</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie węzły chłonne wnęki płuca prawego średnicy do 14mm, SUV max 5,4.  Wnęka płuca lewego SUV max 3,6. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Pęcherz rozedmowy 10mm w segm. 1+2 płuca lewego, nadprzeponowo niewielkie pasmowate zmiany bliznowato-włókniste.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie naciek obejmujący część przedodźwiernikowej żołądka, dwunastnicę, przyległy miąższ płata lewego wątroby i pęcherzyka żółciowego na łącznym obszarze wg PET 162x86x74mm, SUV max do 33,0. Drobny aktywny metabolicznie obszar w żołądku na krzywiźnie większej średnicy wg PET 33mm, SUV max 6,5. Liczne aktywne metabolicznie obszary w topografii jelit średnicy wg PET do 46mm, SUV max do 16,3 - w pierwszej kolejności nacieki chłoniakowe Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Prostata wielkości 58x59mm.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa z cechami dyskopatii wielopoziomowo. Zmiany zwyrodnieniowe w stawach ramiennych, mniej nasilone w stawach biodrowych.  Inne: Miażdżyca aorty i tętnic potomnych.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono rozległy naciek chłoniakowy obejmujący część przedodźwiernikową żołądka, dwunastnicę, przyległy miąższ płata lewego wątroby i pęcherzyka żółciowego, aktywne metabolicznie nacieki w obrębie jelit, żołądka oraz aktywne metabolicznie węzły chłonne wnęki płuca prawego.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>33</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57min od podania 18F-FDG. Glikemia: 92mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony,  miernie nasilony zanik korowo-podkorowy mózgu. Niewielkie okrężne zgrubienia błony śluzowej w lewej zatoce szczękowej.  Klatka piersiowa i śródpiersie: Pobudzony metabolicznie obszar we wnęce płuca prawego średnicy 10mm, SUV max 3,5 - węzeł chłonny? Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Aorta wstępująca o szerokości 42mm. Pęcherz rozedmowy śr. 14mm w segm. 1+2/3 płuca lewego. Drobne obwodowe zmiany włókniste w płacie górnym płuca prawego i lewego. Wydatne pasmowate zmiany włókniste obustronnie nadprzeponowo. Obszary o typie "mlecznej szyby" nadprzeponowo w płucu prawym.  Brzuch i miednica: Aktywny metabolicznie obszar w części przedodźwiernikowej żołądka, wielkości 29mm wg PET, SUV max 5,9, ze zwężeniem kanału odźwiernika i zaleganiem treści żołądkowej. Niejednorodny metabolizm FDG w wątrobie zwłaszcza w s. 4 z wyróżniającym się podtorebkowo obszarem wielkości 10mm wg PET, SUV max 4,7- do oceny w badaniu TK/MR z kontrastem dożylnym. Rozlana i odcinkowo zwiększona aktywnośc metaboliczna w topografii pętli jelitowych - do oceny w kolonoskopii ze względu na opisywane poprzednio nacieki chłoniakowe.  Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nerki o "pozaciąganych" pozapalnie obrysach. Drobny uwapniony konkrement w UKM-ie nerki prawej. Prostata powiększona, wielkości: 65x59mm, wpukla się w obręb pęcherza moczowego - do kontroli urologicznej.  Układ kostny: Zwiększony metabolizm FDG w układzie kostnym- w pierwszej kolejności w związku ze stosowanym leczeniem. Nasilone zmiany zwyrodnieniowo-wytwórcze kręgosłupa.  Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa. Wielopoziomowo nierówne obrysy blaszek granicznych trzonów kręgowych i drobne guzki Schmorla. Drobna spondylolisteza przednia na poziomie L4/L5. Zmiany zwyrodnieniowo-wywtórcze w małych stawach mizykręgowych i w stawach żebrowo-poprzecznych. Zmiany zwyrodnieniowe w stawach ramiennych oraz mniej nasilone w stawach biodrowych. Wydatna wyspa kostna w przymostkowym końcu prawego obojczyka.  Inne: Nasilona miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax do 2,5; Prawy płat wątroby SUVmax do 3,4.</t>
+          <t>92</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony,  miernie nasilony zanik korowo-podkorowy mózgu. Niewielkie okrężne zgrubienia błony śluzowej w lewej zatoce szczękowej.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Pobudzony metabolicznie obszar we wnęce płuca prawego średnicy 10mm, SUV max 3,5 - węzeł chłonny? Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Aorta wstępująca o szerokości 42mm. Pęcherz rozedmowy śr. 14mm w segm. 1+2/3 płuca lewego. Drobne obwodowe zmiany włókniste w płacie górnym płuca prawego i lewego. Wydatne pasmowate zmiany włókniste obustronnie nadprzeponowo. Obszary o typie "mlecznej szyby" nadprzeponowo w płucu prawym.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie obszar w części przedodźwiernikowej żołądka, wielkości 29mm wg PET, SUV max 5,9, ze zwężeniem kanału odźwiernika i zaleganiem treści żołądkowej. Niejednorodny metabolizm FDG w wątrobie zwłaszcza w s. 4 z wyróżniającym się podtorebkowo obszarem wielkości 10mm wg PET, SUV max 4,7- do oceny w badaniu TK/MR z kontrastem dożylnym. Rozlana i odcinkowo zwiększona aktywnośc metaboliczna w topografii pętli jelitowych - do oceny w kolonoskopii ze względu na opisywane poprzednio nacieki chłoniakowe.  Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nerki o "pozaciąganych" pozapalnie obrysach. Drobny uwapniony konkrement w UKM-ie nerki prawej. Prostata powiększona, wielkości: 65x59mm, wpukla się w obręb pęcherza moczowego - do kontroli urologicznej.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Zwiększony metabolizm FDG w układzie kostnym- w pierwszej kolejności w związku ze stosowanym leczeniem. Nasilone zmiany zwyrodnieniowo-wytwórcze kręgosłupa.  Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa. Wielopoziomowo nierówne obrysy blaszek granicznych trzonów kręgowych i drobne guzki Schmorla. Drobna spondylolisteza przednia na poziomie L4/L5. Zmiany zwyrodnieniowo-wywtórcze w małych stawach mizykręgowych i w stawach żebrowo-poprzecznych. Zmiany zwyrodnieniowe w stawach ramiennych oraz mniej nasilone w stawach biodrowych. Wydatna wyspa kostna w przymostkowym końcu prawego obojczyka.  Inne: Nasilona miażdżyca aorty i tętnic potomnych.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono dobrą odpowiedź metaboliczną choroby chłoniakowej na stosowane leczenie. Aktywny metabolicznie obszar w części przedodźwiernikowej żołądka - masa resztkowa?- do weryfikacji w gastroskopii. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>5.9</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 58 min od podania 18F-FDG. Glikemia: 112 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Drobny obszar wzmożonego metabolizmu FDG w śliniance przyusznej lewej średnicy 10 mm wg PET SUV max 3,9-węzeł własny? -  do kontroli w USG. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony,  miernie nasilony zanik korowo-podkorowy mózgu. Dyskretne zgrubienia błony śluzowej w zachyłku zębodołowym lewej zatoki szczękowej.  Klatka piersiowa i śródpiersie: Wzmożony metabolizm FDG we wnęce płuca prawego SUV max do 5,8 - w stosunku do wnęki płuca lewego SUV max do 3,4. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Znacznego stopnia zaleganie treści płynnej w żołądku [ze znacznym jego poszerzeniem - żołądek wypełnia w znacznym stopniu nadbrzusze i śródbrzusze oraz z pogrubieniem ściany w części przedodźwiernikowej i okolicy odźwiernika] oraz w 1/2 dolnej części przełyku [z jego poszerzeniem do 38mm] - celowa kontrola gastrologiczna/gastroskopowa. Aorta wstępująca o szerokości 42mm. Pęcherz rozedmowy śr. 14mm w segm. 1+2/3 płuca lewego. Ok. 3,5mm obwodowy uwapniony guzek w segm. 3 płuca prawego. Drobne obwodowe zmiany włókniste i pojedyncze drobnoguzkowe w płacie górnym płuca prawego i lewego. Niewielkie zmiany włókniste w segm. 5 obu płuc. Wydatne pasmowate zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Aktywny metabolicznie naciek w topografii połączenia odbytniczo-esiczego na obszarze wielkości 15x26 mm wg PET SUV max 14,3 - do pilnej weryfikacji w badaniu endoskopowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nerki o "pozaciąganych" pozapalnie obrysach. Drobny uwapniony konkrement w UKM-ie nerki prawej. Prostata powiększona, wielkości: 65x59mm, wpukla się w obręb pęcherza moczowego - do kontroli urologicznej.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Nasilone zmiany zwyrodnieniowo-wytwórcze kręgosłupa.  Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa.  Wielopoziomowo nierówne obrysy blaszek granicznych trzonów kręgowych i drobne guzki Schmorla. Drobna spondylolisteza przednia na poziomie L4/L5. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Zmiany zwyrodnieniowe w stawach ramiennych oraz mniej nasilone w stawach biodrowych. Wydatna wyspa kostna w przymostkowym końcu prawego obojczyka.  Inne: Nasilona miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax do 2,1; Prawy płat wątroby SUVmax do 3,1.</t>
+          <t>112</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Drobny obszar wzmożonego metabolizmu FDG w śliniance przyusznej lewej średnicy 10 mm wg PET SUV max 3,9-węzeł własny? -  do kontroli w USG. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Uogólniony,  miernie nasilony zanik korowo-podkorowy mózgu. Dyskretne zgrubienia błony śluzowej w zachyłku zębodołowym lewej zatoki szczękowej.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Wzmożony metabolizm FDG we wnęce płuca prawego SUV max do 5,8 - w stosunku do wnęki płuca lewego SUV max do 3,4. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Znacznego stopnia zaleganie treści płynnej w żołądku [ze znacznym jego poszerzeniem - żołądek wypełnia w znacznym stopniu nadbrzusze i śródbrzusze oraz z pogrubieniem ściany w części przedodźwiernikowej i okolicy odźwiernika] oraz w 1/2 dolnej części przełyku [z jego poszerzeniem do 38mm] - celowa kontrola gastrologiczna/gastroskopowa. Aorta wstępująca o szerokości 42mm. Pęcherz rozedmowy śr. 14mm w segm. 1+2/3 płuca lewego. Ok. 3,5mm obwodowy uwapniony guzek w segm. 3 płuca prawego. Drobne obwodowe zmiany włókniste i pojedyncze drobnoguzkowe w płacie górnym płuca prawego i lewego. Niewielkie zmiany włókniste w segm. 5 obu płuc. Wydatne pasmowate zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie naciek w topografii połączenia odbytniczo-esiczego na obszarze wielkości 15x26 mm wg PET SUV max 14,3 - do pilnej weryfikacji w badaniu endoskopowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Nerki o "pozaciąganych" pozapalnie obrysach. Drobny uwapniony konkrement w UKM-ie nerki prawej. Prostata powiększona, wielkości: 65x59mm, wpukla się w obręb pęcherza moczowego - do kontroli urologicznej.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Nasilone zmiany zwyrodnieniowo-wytwórcze kręgosłupa.  Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku szyjnym, piersiowym i lędźwiowym kręgosłupa.  Wielopoziomowo nierówne obrysy blaszek granicznych trzonów kręgowych i drobne guzki Schmorla. Drobna spondylolisteza przednia na poziomie L4/L5. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Zmiany zwyrodnieniowe w stawach ramiennych oraz mniej nasilone w stawach biodrowych. Wydatna wyspa kostna w przymostkowym końcu prawego obojczyka.  Inne: Nasilona miażdżyca aorty i tętnic potomnych.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnego metabolicznie nacieku w topografii połączenia odbytniczo-esiczego - do pilnej weryfikacji w badaniu endoskopowym. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>14.3</v>
       </c>
     </row>
